--- a/tools/fixtures/po-import-wip-sample.xlsx
+++ b/tools/fixtures/po-import-wip-sample.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">WIP part A</t>
   </si>
   <si>
-    <t xml:space="preserve">18/08/2026</t>
+    <t xml:space="preserve">27/08/2026</t>
   </si>
   <si>
     <t xml:space="preserve">07:00</t>
